--- a/KIJ/CO_CH4/VLE_CO_CH4.xlsx
+++ b/KIJ/CO_CH4/VLE_CO_CH4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\darshanraju\OneDrive - Delft University of Technology\Desktop\A6\KIJ\CO_CH4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677896E5-C1DB-421E-80B0-3853D831A89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8476BD44-1ED3-4D68-8BFB-BAD33770E288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
     <t>CO</t>
   </si>
   <si>
-    <t>Christiansen, L. J.; Fredenslund, A.; Mollerup, J. M. Cryogenics, 1973, 13, 405 Vapor-liquid equilibrium of the methane - argon, methane - carbon monoxide, and argon - carbon monoxide systems at elevated pressures</t>
+    <t>Christiansen et, al (1973)</t>
   </si>
 </sst>
 </file>
@@ -106,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -125,9 +125,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -447,16 +444,16 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2" s="3">
         <v>3.6379999999999999</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="3">
         <v>0.05</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="3">
         <v>0.34599999999999997</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="3">
         <v>123.41330000000001</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -467,16 +464,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="3">
         <v>5.0049999999999999</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="3">
         <v>0.11899999999999999</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="3">
         <v>0.54200000000000004</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="3">
         <v>123.41330000000001</v>
       </c>
       <c r="E3" s="6" t="s">
@@ -487,16 +484,16 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="A4" s="3">
         <v>6.9909999999999997</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="3">
         <v>0.20699999999999999</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="3">
         <v>0.68799999999999994</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="3">
         <v>123.41330000000001</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -507,16 +504,16 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="3">
         <v>9.8789999999999996</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="3">
         <v>0.36</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="3">
         <v>0.8</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="3">
         <v>123.41330000000001</v>
       </c>
       <c r="E5" s="6" t="s">
@@ -527,16 +524,16 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="3">
         <v>12.848000000000001</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="3">
         <v>0.53800000000000003</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="3">
         <v>0.86499999999999999</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="3">
         <v>123.41330000000001</v>
       </c>
       <c r="E6" s="6" t="s">
@@ -547,16 +544,16 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="3">
         <v>15.878</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="3">
         <v>0.72099999999999997</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="3">
         <v>0.91600000000000004</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="3">
         <v>123.41330000000001</v>
       </c>
       <c r="E7" s="6" t="s">
@@ -567,16 +564,16 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="3">
         <v>18.178000000000001</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="3">
         <v>0.84199999999999997</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="3">
         <v>0.94699999999999995</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="3">
         <v>123.41330000000001</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -587,16 +584,16 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="3">
         <v>20.245000000000001</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="3">
         <v>0.92600000000000005</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="3">
         <v>0.97499999999999998</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="3">
         <v>123.41330000000001</v>
       </c>
       <c r="E9" s="6" t="s">
@@ -607,16 +604,16 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10" s="3">
         <v>21.318999999999999</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="3">
         <v>0.96599999999999997</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="3">
         <v>0.98799999999999999</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="3">
         <v>123.41330000000001</v>
       </c>
       <c r="E10" s="6" t="s">
@@ -627,16 +624,16 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="3">
         <v>6.9909999999999997</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="3">
         <v>0.04</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="3">
         <v>0.20599999999999999</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="3">
         <v>137.114</v>
       </c>
       <c r="E11" s="6" t="s">
@@ -647,16 +644,16 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12" s="3">
         <v>8.7040000000000006</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="3">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="3">
         <v>0.38100000000000001</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="3">
         <v>137.114</v>
       </c>
       <c r="E12" s="6" t="s">
@@ -667,16 +664,16 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="3">
         <v>13</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="3">
         <v>0.221</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="3">
         <v>0.59599999999999997</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="3">
         <v>137.114</v>
       </c>
       <c r="E13" s="6" t="s">
@@ -687,16 +684,16 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14" s="3">
         <v>16.687999999999999</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="3">
         <v>0.32800000000000001</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="3">
         <v>0.7</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="3">
         <v>137.114</v>
       </c>
       <c r="E14" s="6" t="s">
@@ -707,16 +704,16 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="A15" s="3">
         <v>20.599</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="3">
         <v>0.45</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="3">
         <v>0.77100000000000002</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="3">
         <v>137.114</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -727,16 +724,16 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+      <c r="A16" s="3">
         <v>24.541</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="3">
         <v>0.58699999999999997</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="3">
         <v>0.82499999999999996</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="3">
         <v>137.114</v>
       </c>
       <c r="E16" s="6" t="s">
@@ -751,16 +748,16 @@
       <c r="J16" s="2"/>
     </row>
     <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="3">
         <v>28.765999999999998</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="3">
         <v>0.73</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="3">
         <v>0.86799999999999999</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="3">
         <v>137.114</v>
       </c>
       <c r="E17" s="6" t="s">
@@ -779,16 +776,16 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
+      <c r="A18" s="3">
         <v>31.815999999999999</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="3">
         <v>0.80800000000000005</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="3">
         <v>0.89700000000000002</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="3">
         <v>137.114</v>
       </c>
       <c r="E18" s="6" t="s">
@@ -807,16 +804,16 @@
       <c r="O18" s="3"/>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="A19" s="3">
         <v>33.548999999999999</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="3">
         <v>0.85199999999999998</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="3">
         <v>0.91200000000000003</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="3">
         <v>137.114</v>
       </c>
       <c r="E19" s="6" t="s">
@@ -835,16 +832,16 @@
       <c r="O19" s="3"/>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
+      <c r="A20" s="3">
         <v>35.473999999999997</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="3">
         <v>0.89200000000000002</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="3">
         <v>0.92600000000000005</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="3">
         <v>137.114</v>
       </c>
       <c r="E20" s="6" t="s">
@@ -864,16 +861,16 @@
       <c r="O20" s="3"/>
     </row>
     <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
+      <c r="A21" s="3">
         <v>20.902999999999999</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="3">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="3">
         <v>0.104</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="3">
         <v>164.0136</v>
       </c>
       <c r="E21" s="6" t="s">
@@ -893,16 +890,16 @@
       <c r="O21" s="3"/>
     </row>
     <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
+      <c r="A22" s="3">
         <v>23.436</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="3">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="3">
         <v>0.19700000000000001</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="3">
         <v>164.0136</v>
       </c>
       <c r="E22" s="6" t="s">
@@ -922,16 +919,16 @@
       <c r="O22" s="3"/>
     </row>
     <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
+      <c r="A23" s="3">
         <v>26.414999999999999</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="3">
         <v>0.12</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="3">
         <v>0.28100000000000003</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="3">
         <v>164.0136</v>
       </c>
       <c r="E23" s="6" t="s">
@@ -951,16 +948,16 @@
       <c r="O23" s="3"/>
     </row>
     <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
+      <c r="A24" s="3">
         <v>31.937999999999999</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="3">
         <v>0.21199999999999999</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="3">
         <v>0.38900000000000001</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="3">
         <v>164.0136</v>
       </c>
       <c r="E24" s="6" t="s">
@@ -980,16 +977,16 @@
       <c r="O24" s="3"/>
     </row>
     <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
+      <c r="A25" s="3">
         <v>37.207000000000001</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="3">
         <v>0.29399999999999998</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="3">
         <v>0.46</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="3">
         <v>164.0136</v>
       </c>
       <c r="E25" s="6" t="s">
@@ -1009,16 +1006,16 @@
       <c r="O25" s="3"/>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
+      <c r="A26" s="3">
         <v>41.594000000000001</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="3">
         <v>0.36099999999999999</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="3">
         <v>0.499</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="3">
         <v>164.0136</v>
       </c>
       <c r="E26" s="6" t="s">
@@ -1038,16 +1035,16 @@
       <c r="O26" s="3"/>
     </row>
     <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
+      <c r="A27" s="3">
         <v>45.576000000000001</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="3">
         <v>0.42899999999999999</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="3">
         <v>0.51800000000000002</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="3">
         <v>164.0136</v>
       </c>
       <c r="E27" s="6" t="s">
@@ -1067,16 +1064,16 @@
       <c r="O27" s="3"/>
     </row>
     <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
+      <c r="A28" s="3">
         <v>46.609000000000002</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="3">
         <v>0.45200000000000001</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="3">
         <v>0.51</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="3">
         <v>164.0136</v>
       </c>
       <c r="E28" s="6" t="s">
@@ -1096,16 +1093,16 @@
       <c r="O28" s="3"/>
     </row>
     <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
+      <c r="A29" s="3">
         <v>33.012</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="3">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="3">
         <v>178.01220000000001</v>
       </c>
       <c r="E29" s="6" t="s">
@@ -1121,16 +1118,16 @@
       <c r="K29" s="3"/>
     </row>
     <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
+      <c r="A30" s="3">
         <v>36.072000000000003</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="3">
         <v>6.2E-2</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="3">
         <v>0.125</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="3">
         <v>178.01220000000001</v>
       </c>
       <c r="E30" s="6" t="s">
@@ -1150,16 +1147,16 @@
       <c r="O30" s="2"/>
     </row>
     <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
+      <c r="A31" s="3">
         <v>38.847999999999999</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="3">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="3">
         <v>0.17599999999999999</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="3">
         <v>178.01220000000001</v>
       </c>
       <c r="E31" s="6" t="s">
@@ -1179,16 +1176,16 @@
       <c r="O31" s="3"/>
     </row>
     <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
+      <c r="A32" s="3">
         <v>42.262999999999998</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="3">
         <v>0.13900000000000001</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="3">
         <v>0.223</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="3">
         <v>178.01220000000001</v>
       </c>
       <c r="E32" s="6" t="s">
@@ -1207,16 +1204,16 @@
       <c r="O32" s="3"/>
     </row>
     <row r="33" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
+      <c r="A33" s="3">
         <v>45.505000000000003</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="3">
         <v>0.184</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="3">
         <v>0.252</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="3">
         <v>178.01220000000001</v>
       </c>
       <c r="E33" s="6" t="s">
@@ -1240,16 +1237,16 @@
       <c r="S33" s="2"/>
     </row>
     <row r="34" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
+      <c r="A34" s="3">
         <v>47.39</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="3">
         <v>0.21299999999999999</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="3">
         <v>0.26100000000000001</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="3">
         <v>178.01220000000001</v>
       </c>
       <c r="E34" s="6" t="s">
